--- a/public/exports-from-60-with-coowners/29189609.xlsx
+++ b/public/exports-from-60-with-coowners/29189609.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010715</t>
+          <t xml:space="preserve">200010720</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -22564,12 +22564,12 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419877</t>
+          <t xml:space="preserve">311419878</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311420218</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189609.xlsx
+++ b/public/exports-from-60-with-coowners/29189609.xlsx
@@ -21791,30 +21791,30 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J291">
-        <v>788</v>
+        <v>1856</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389420</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21881,11 +21881,11 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J292">
-        <v>1856</v>
+        <v>2960</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -21956,11 +21956,11 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J293">
-        <v>2960</v>
+        <v>1091</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -22031,11 +22031,11 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J294">
-        <v>1091</v>
+        <v>380</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -22106,11 +22106,11 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J295">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -22181,11 +22181,11 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J296">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -22241,30 +22241,30 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Tøstrupvej 26</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>447</v>
+        <v>2185</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22316,17 +22316,17 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøstrupvej 26</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,11 +22335,11 @@
         </is>
       </c>
       <c r="J298">
-        <v>2185</v>
+        <v>655</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22406,11 +22406,11 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J299">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -22466,17 +22466,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Engdraget 24A</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -22485,21 +22485,21 @@
         </is>
       </c>
       <c r="J300">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311419880</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 24A</t>
+          <t xml:space="preserve">Engdraget 26A</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J301">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419878</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 26A</t>
+          <t xml:space="preserve">Bindesbølvej 2</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22626,30 +22626,30 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">4466575</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J302">
-        <v>390</v>
+        <v>209</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420218</t>
+          <t xml:space="preserve">311424214</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbølvej 2</t>
+          <t xml:space="preserve">Skjernåvej 4A</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466575</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,11 +22710,11 @@
         </is>
       </c>
       <c r="J303">
-        <v>209</v>
+        <v>399</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424214</t>
+          <t xml:space="preserve">311424140</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22766,17 +22766,17 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjernåvej 4A</t>
+          <t xml:space="preserve">Svinget 5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -22785,21 +22785,21 @@
         </is>
       </c>
       <c r="J304">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424140</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22856,11 +22856,11 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J305">
-        <v>392</v>
+        <v>703</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -22916,30 +22916,30 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 5</t>
+          <t xml:space="preserve">Centerparken 1</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">9701346</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J306">
-        <v>703</v>
+        <v>4482</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311552774</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,17 +22991,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centerparken 1</t>
+          <t xml:space="preserve">Jægervej 13</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9701346</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -23010,11 +23010,11 @@
         </is>
       </c>
       <c r="J307">
-        <v>4482</v>
+        <v>1557</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552774</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-04</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 13</t>
+          <t xml:space="preserve">Lærkevænget 1</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -23085,11 +23085,11 @@
         </is>
       </c>
       <c r="J308">
-        <v>1557</v>
+        <v>417</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23141,17 +23141,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevænget 1</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -23160,11 +23160,11 @@
         </is>
       </c>
       <c r="J309">
-        <v>417</v>
+        <v>1060</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311555859</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23216,17 +23216,17 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -23235,11 +23235,11 @@
         </is>
       </c>
       <c r="J310">
-        <v>1060</v>
+        <v>606</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555859</t>
+          <t xml:space="preserve">311561693</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23291,17 +23291,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Storegade 40</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4467758</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -23310,11 +23310,11 @@
         </is>
       </c>
       <c r="J311">
-        <v>606</v>
+        <v>401</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561693</t>
+          <t xml:space="preserve">311599352</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-13</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23366,17 +23366,17 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40</t>
+          <t xml:space="preserve">Åvænget 3A</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467758</t>
+          <t xml:space="preserve">100145225</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -23385,11 +23385,11 @@
         </is>
       </c>
       <c r="J312">
-        <v>401</v>
+        <v>810</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599352</t>
+          <t xml:space="preserve">311582272</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,17 +23441,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åvænget 3A</t>
+          <t xml:space="preserve">Nygade 1</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">100145225</t>
+          <t xml:space="preserve">4467959</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -23460,11 +23460,11 @@
         </is>
       </c>
       <c r="J313">
-        <v>810</v>
+        <v>308</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582272</t>
+          <t xml:space="preserve">311598466</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23501,12 +23501,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -23516,40 +23516,40 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 1</t>
+          <t xml:space="preserve">Vesterled 6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467959</t>
+          <t xml:space="preserve">746440, 7003908</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J314">
-        <v>308</v>
+        <v>146</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598466</t>
+          <t xml:space="preserve">311605015</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23576,12 +23576,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -23591,40 +23591,40 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 6</t>
+          <t xml:space="preserve">Midtbyvej 30</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">746440, 7003908</t>
+          <t xml:space="preserve">7662602</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J315">
-        <v>146</v>
+        <v>1817</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605015</t>
+          <t xml:space="preserve">311650708</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MST-Bygtjek ApS</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,40 +23666,40 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 30</t>
+          <t xml:space="preserve">Holmegaardsbakken 18</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">7662602</t>
+          <t xml:space="preserve">335032</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J316">
-        <v>1817</v>
+        <v>116</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650708</t>
+          <t xml:space="preserve">311653077</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">MST-Bygtjek ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23726,12 +23726,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">bomidtvest</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -23741,30 +23741,30 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 18</t>
+          <t xml:space="preserve">Tarmvej 99</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">335032</t>
+          <t xml:space="preserve">337849, 337850</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J317">
-        <v>116</v>
+        <v>878</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653077</t>
+          <t xml:space="preserve">311668912</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23801,12 +23801,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">bomidtvest</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -23816,40 +23816,40 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarmvej 99</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">337849, 337850</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J318">
-        <v>878</v>
+        <v>99</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668912</t>
+          <t xml:space="preserve">311679352</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,30 +23891,30 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J319">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679352</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23966,40 +23966,40 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Ranunkelvej 11A</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">5790131, 100782857</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J320">
-        <v>100</v>
+        <v>414</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679351</t>
+          <t xml:space="preserve">311689382</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,40 +24041,40 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 11A</t>
+          <t xml:space="preserve">Skolebakken 20</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131, 100782857</t>
+          <t xml:space="preserve">746445, 4419703</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J321">
-        <v>414</v>
+        <v>3326</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689382</t>
+          <t xml:space="preserve">311883390</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2036-02-21</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,30 +24116,30 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 20</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">746445, 4419703</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J322">
-        <v>3326</v>
+        <v>1345</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883390</t>
+          <t xml:space="preserve">311886105</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-21</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24206,15 +24206,15 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J323">
-        <v>1345</v>
+        <v>2810</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886105</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24281,15 +24281,15 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J324">
-        <v>2810</v>
+        <v>1725</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311886107</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24356,15 +24356,15 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J325">
-        <v>1725</v>
+        <v>1360</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886107</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24416,17 +24416,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -24435,21 +24435,21 @@
         </is>
       </c>
       <c r="J326">
-        <v>1360</v>
+        <v>703</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311889055</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,40 +24491,40 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J327">
-        <v>703</v>
+        <v>125</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311889055</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24581,11 +24581,11 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J328">
-        <v>125</v>
+        <v>766</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -24656,11 +24656,11 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J329">
-        <v>766</v>
+        <v>241</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
@@ -24731,15 +24731,15 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J330">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311892268</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24806,11 +24806,11 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J331">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -24866,30 +24866,30 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J332">
-        <v>178</v>
+        <v>2123</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24956,11 +24956,11 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J333">
-        <v>2123</v>
+        <v>915</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
@@ -25031,11 +25031,11 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J334">
-        <v>915</v>
+        <v>616</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
@@ -25106,11 +25106,11 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J335">
-        <v>616</v>
+        <v>1810</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
@@ -25181,11 +25181,11 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J336">
-        <v>1810</v>
+        <v>125</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -25256,11 +25256,11 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J337">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
@@ -25316,35 +25316,35 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">746506, 4477641</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J338">
-        <v>128</v>
+        <v>2072</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892347</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -25391,17 +25391,17 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Ågade 12</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">746506, 4477641</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -25410,16 +25410,16 @@
         </is>
       </c>
       <c r="J339">
-        <v>2072</v>
+        <v>729</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892347</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 12</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J340">
@@ -25541,17 +25541,17 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Badevej 17A</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">4421290, 100992804</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -25560,21 +25560,21 @@
         </is>
       </c>
       <c r="J341">
-        <v>729</v>
+        <v>370</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311900271</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-05-10</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,40 +25616,40 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Badevej 17A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421290, 100992804</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J342">
-        <v>370</v>
+        <v>788</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900271</t>
+          <t xml:space="preserve">311929041</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-10</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189609.xlsx
+++ b/public/exports-from-60-with-coowners/29189609.xlsx
@@ -8441,26 +8441,26 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 10</t>
+          <t xml:space="preserve">Klostervej 3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">746491, 8463749</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J113">
-        <v>178</v>
+        <v>1396</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8516,26 +8516,26 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J114">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8591,26 +8591,26 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 65</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J115">
-        <v>232</v>
+        <v>2567</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8666,26 +8666,26 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 65</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J116">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,26 +8741,26 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 67A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>232</v>
+        <v>8744</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8816,26 +8816,26 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 67A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>160</v>
+        <v>1430</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,26 +8891,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kongevej 46</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">5791577</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,26 +8966,26 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kongevej 46</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">5791577</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J120">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9041,26 +9041,26 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kroghedevej 2A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J121">
-        <v>735</v>
+        <v>1035</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9116,26 +9116,26 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kroghedevej 2A</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J122">
-        <v>153</v>
+        <v>339</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kærbyvej 1B</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,16 +9201,16 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746457, 10181520</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Lybækvej 14A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,16 +9276,16 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">10009013</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>237</v>
+        <v>90</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,26 +9341,26 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 3</t>
+          <t xml:space="preserve">Lybækvej 14A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">10009013</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>1396</v>
+        <v>406</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 3</t>
+          <t xml:space="preserve">Lønborgvej 53</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,16 +9426,16 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">4468195</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>320</v>
+        <v>5216</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 65</t>
+          <t xml:space="preserve">Mellemgade 23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,16 +9501,16 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>2567</v>
+        <v>664</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9566,26 +9566,26 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 65</t>
+          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">746733, 9329112</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>380</v>
+        <v>765</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 67A</t>
+          <t xml:space="preserve">Nygade 48</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,16 +9651,16 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">100098945</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>8744</v>
+        <v>1535</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 67A</t>
+          <t xml:space="preserve">Nygade 50A</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,16 +9726,16 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">100287180</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>1430</v>
+        <v>340</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 46</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5791577</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="J131">
-        <v>202</v>
+        <v>2175</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 46</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5791577</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="J132">
-        <v>71</v>
+        <v>362</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9941,26 +9941,26 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kroghedevej 2A</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J133">
-        <v>1035</v>
+        <v>328</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10016,26 +10016,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kroghedevej 2A</t>
+          <t xml:space="preserve">Nørlundvej 3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">100361476</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J134">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10091,26 +10091,26 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærbyvej 1B</t>
+          <t xml:space="preserve">Nørlundvej 7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">746457, 10181520</t>
+          <t xml:space="preserve">7879617</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>160</v>
+        <v>635</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lybækvej 14A</t>
+          <t xml:space="preserve">Nørregade 84</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10009013</t>
+          <t xml:space="preserve">4416989</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="J136">
-        <v>90</v>
+        <v>855</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lybækvej 14A</t>
+          <t xml:space="preserve">Nørregade 88</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10009013</t>
+          <t xml:space="preserve">746342, 4414222</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>406</v>
+        <v>353</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønborgvej 53</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468195</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="J138">
-        <v>5216</v>
+        <v>262</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,26 +10391,26 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 23</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J139">
-        <v>664</v>
+        <v>276</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10466,26 +10466,26 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">746733, 9329112</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J140">
-        <v>765</v>
+        <v>256</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10541,26 +10541,26 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 48</t>
+          <t xml:space="preserve">Parallelvej 301</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100098945</t>
+          <t xml:space="preserve">100060251</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>1535</v>
+        <v>1021</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 50A</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,16 +10626,16 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100287180</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J142">
-        <v>340</v>
+        <v>920</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10691,26 +10691,26 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J143">
-        <v>2175</v>
+        <v>2717</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10766,26 +10766,26 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J144">
-        <v>362</v>
+        <v>1531</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,26 +10841,26 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J145">
-        <v>328</v>
+        <v>3165</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10916,26 +10916,26 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 3</t>
+          <t xml:space="preserve">Ranunkelvej 15</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100361476</t>
+          <t xml:space="preserve">746579, 5790131</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J146">
-        <v>371</v>
+        <v>146</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10991,26 +10991,26 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 7</t>
+          <t xml:space="preserve">Ranunkelvej 5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7879617</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J147">
-        <v>635</v>
+        <v>740</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11066,26 +11066,26 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 84</t>
+          <t xml:space="preserve">Ranunkelvej 7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416989</t>
+          <t xml:space="preserve">5790131</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>855</v>
+        <v>7967</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 88</t>
+          <t xml:space="preserve">Skelmosevej 20B</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">746342, 4414222</t>
+          <t xml:space="preserve">100069203</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="J149">
-        <v>353</v>
+        <v>115</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11216,26 +11216,26 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J150">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="J151">
-        <v>276</v>
+        <v>1259</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11366,26 +11366,26 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J152">
-        <v>256</v>
+        <v>1728</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11441,26 +11441,26 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 301</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060251</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J153">
-        <v>1021</v>
+        <v>242</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,26 +11516,26 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J154">
-        <v>920</v>
+        <v>704</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11591,26 +11591,26 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>2717</v>
+        <v>472</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,26 +11666,26 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>1531</v>
+        <v>447</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11741,26 +11741,26 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J157">
-        <v>3165</v>
+        <v>1502</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11816,26 +11816,26 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 15</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">746579, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J158">
-        <v>146</v>
+        <v>266</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11891,26 +11891,26 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 5</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J159">
-        <v>740</v>
+        <v>273</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11966,26 +11966,26 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 7</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131</t>
+          <t xml:space="preserve">4471273</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>7967</v>
+        <v>1021</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelmosevej 20B</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069203</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="J161">
-        <v>115</v>
+        <v>698</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="J162">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12191,26 +12191,26 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>1259</v>
+        <v>1606</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,26 +12266,26 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J164">
-        <v>1728</v>
+        <v>516</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12341,26 +12341,26 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skolevænget 31B</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J165">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12416,26 +12416,26 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J166">
-        <v>704</v>
+        <v>209</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12491,26 +12491,26 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J167">
-        <v>472</v>
+        <v>195</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12566,26 +12566,26 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Skovvej 29</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">100064416</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J168">
-        <v>447</v>
+        <v>1014</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12641,26 +12641,26 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Skyggehusvej 2A</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J169">
-        <v>1502</v>
+        <v>2728</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,26 +12716,26 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Skyggehusvej 2A</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J170">
-        <v>266</v>
+        <v>1122</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12791,26 +12791,26 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Smed Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">8918730</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J171">
-        <v>273</v>
+        <v>1946</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12866,26 +12866,26 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4471273</t>
+          <t xml:space="preserve">746471, 5725286</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>1021</v>
+        <v>1793</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12941,17 +12941,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Storegade 40A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4468042</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="J173">
-        <v>698</v>
+        <v>152</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,16 +13026,16 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">746565, 4481209</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="J174">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,16 +13101,16 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J175">
-        <v>1606</v>
+        <v>266</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="J176">
-        <v>516</v>
+        <v>190</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31B</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,16 +13251,16 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J177">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13316,26 +13316,26 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Svinget 4A</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">5788486</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13391,17 +13391,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="J179">
-        <v>195</v>
+        <v>468</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13466,26 +13466,26 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 29</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064416</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J180">
-        <v>1014</v>
+        <v>2597</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,26 +13541,26 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyggehusvej 2A</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J181">
-        <v>2728</v>
+        <v>70</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13616,26 +13616,26 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyggehusvej 2A</t>
+          <t xml:space="preserve">Torvegade 20A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">9037914</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>1122</v>
+        <v>1284</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 1</t>
+          <t xml:space="preserve">Torvet 22</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,16 +13701,16 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918730</t>
+          <t xml:space="preserve">5724727</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>1946</v>
+        <v>606</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13766,26 +13766,26 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
+          <t xml:space="preserve">Tylvadvej 2B</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">746471, 5725286</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>1793</v>
+        <v>2572</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13841,26 +13841,26 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40A</t>
+          <t xml:space="preserve">Tylvadvej 2B</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468042</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J185">
-        <v>152</v>
+        <v>1285</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Tylvadvej 2C</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,16 +13926,16 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">746565, 4481209</t>
+          <t xml:space="preserve">746560, 4480243</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J186">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Tømrervej 2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,16 +14001,16 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">5789801</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>266</v>
+        <v>828</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -14066,26 +14066,26 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">V Strandsbjerg 29</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">746437, 5725570</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J188">
-        <v>190</v>
+        <v>355</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -14141,26 +14141,26 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>458</v>
+        <v>2841</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14216,26 +14216,26 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 4A</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788486</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J190">
-        <v>132</v>
+        <v>795</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14291,26 +14291,26 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J191">
-        <v>468</v>
+        <v>2194</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14366,26 +14366,26 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J192">
-        <v>2597</v>
+        <v>825</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14441,26 +14441,26 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J193">
-        <v>70</v>
+        <v>1037</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 20A</t>
+          <t xml:space="preserve">Vardevej 13</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,16 +14526,16 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037914</t>
+          <t xml:space="preserve">4468945</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J194">
-        <v>1284</v>
+        <v>286</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14591,26 +14591,26 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 22</t>
+          <t xml:space="preserve">Vardevej 47A</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724727</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J195">
-        <v>606</v>
+        <v>76</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2B</t>
+          <t xml:space="preserve">Vardevej 86</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">5792712</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="J196">
-        <v>2572</v>
+        <v>216</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14741,26 +14741,26 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2B</t>
+          <t xml:space="preserve">Ved Fjorden 2A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">746456, 5725275</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J197">
-        <v>1285</v>
+        <v>268</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,26 +14816,26 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2C</t>
+          <t xml:space="preserve">Ved Fjorden 2B</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">746560, 4480243</t>
+          <t xml:space="preserve">746458, 8463679</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J198">
-        <v>294</v>
+        <v>375</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tømrervej 2</t>
+          <t xml:space="preserve">Ved Fjorden 6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789801</t>
+          <t xml:space="preserve">5725532</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="J199">
-        <v>828</v>
+        <v>3304</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">V Strandsbjerg 29</t>
+          <t xml:space="preserve">Vesterhavsvej 72</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">746437, 5725570</t>
+          <t xml:space="preserve">7636857</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="J200">
-        <v>355</v>
+        <v>107</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -15041,17 +15041,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="J201">
-        <v>2841</v>
+        <v>69</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15116,17 +15116,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,7 +15135,7 @@
         </is>
       </c>
       <c r="J202">
-        <v>795</v>
+        <v>159</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15191,26 +15191,26 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J203">
-        <v>2194</v>
+        <v>159</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Ågade 2</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,16 +15276,16 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">9221919</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>825</v>
+        <v>3757</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Østerbyvej 3B</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,16 +15351,16 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J205">
-        <v>1037</v>
+        <v>475</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15416,45 +15416,45 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 13</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468945</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>286</v>
+        <v>2202</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200008078</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">PP Rådgivning A/S</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-10-09</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15491,45 +15491,45 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 47A</t>
+          <t xml:space="preserve">Nørrevænget 33</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">8369478</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010715</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-18</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 86</t>
+          <t xml:space="preserve">Vasevej 31</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792712</t>
+          <t xml:space="preserve">5727592</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,26 +15585,26 @@
         </is>
       </c>
       <c r="J208">
-        <v>216</v>
+        <v>821</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010804</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-22</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2A</t>
+          <t xml:space="preserve">Søibergsvej 15</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,35 +15651,35 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">746456, 5725275</t>
+          <t xml:space="preserve">5726357</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>268</v>
+        <v>563</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010845</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-23</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2B</t>
+          <t xml:space="preserve">Vasevej 29</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,35 +15726,35 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">746458, 8463679</t>
+          <t xml:space="preserve">5728667</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>375</v>
+        <v>491</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010944</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 6</t>
+          <t xml:space="preserve">Søibergsvej 13</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725532</t>
+          <t xml:space="preserve">5726356</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,26 +15810,26 @@
         </is>
       </c>
       <c r="J211">
-        <v>3304</v>
+        <v>680</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010984</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-26</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterhavsvej 72</t>
+          <t xml:space="preserve">Bredgade 1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7636857</t>
+          <t xml:space="preserve">4483953</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,26 +15885,26 @@
         </is>
       </c>
       <c r="J212">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011801</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-24</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -15941,45 +15941,45 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J213">
-        <v>69</v>
+        <v>403</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011840</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -16016,45 +16016,45 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Klostervej 33</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">4422741</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>159</v>
+        <v>390</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011821</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16091,45 +16091,45 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Søibergsvej 11</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">5726355</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J215">
-        <v>159</v>
+        <v>529</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011832</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 2</t>
+          <t xml:space="preserve">Engdraget 22</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221919</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,26 +16185,26 @@
         </is>
       </c>
       <c r="J216">
-        <v>3757</v>
+        <v>179</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011880</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -16241,45 +16241,45 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbyvej 3B</t>
+          <t xml:space="preserve">Godthaabsvej 8</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">5725086</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>475</v>
+        <v>746</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011892</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Adelvej 39A</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4419782</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,21 +16335,21 @@
         </is>
       </c>
       <c r="J218">
-        <v>2202</v>
+        <v>419</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008078</t>
+          <t xml:space="preserve">200012873</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-09</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,17 +16391,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 33</t>
+          <t xml:space="preserve">Holmegaardsbakken 22</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369478</t>
+          <t xml:space="preserve">8161686</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>377</v>
+        <v>314</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010720</t>
+          <t xml:space="preserve">200012912</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-18</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 31</t>
+          <t xml:space="preserve">Hvidkløvervej 8</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727592</t>
+          <t xml:space="preserve">9430418</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>821</v>
+        <v>311</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010804</t>
+          <t xml:space="preserve">200012910</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-22</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 15</t>
+          <t xml:space="preserve">Herningvej 31</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726357</t>
+          <t xml:space="preserve">5726882</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>563</v>
+        <v>253</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010845</t>
+          <t xml:space="preserve">200012988</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-23</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 29</t>
+          <t xml:space="preserve">Smedegade 7</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728667</t>
+          <t xml:space="preserve">5724932</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>491</v>
+        <v>216</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010944</t>
+          <t xml:space="preserve">200012990</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 13</t>
+          <t xml:space="preserve">Byskellet 20</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726356</t>
+          <t xml:space="preserve">5725537</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>680</v>
+        <v>1556</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010984</t>
+          <t xml:space="preserve">200013034</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-26</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 1</t>
+          <t xml:space="preserve">Drosselvej 9</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483953</t>
+          <t xml:space="preserve">5792930</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16785,11 +16785,11 @@
         </is>
       </c>
       <c r="J224">
-        <v>195</v>
+        <v>356</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011801</t>
+          <t xml:space="preserve">200013038</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-24</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Fischersvej 6</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4483012</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>403</v>
+        <v>848</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011840</t>
+          <t xml:space="preserve">200012993</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 33</t>
+          <t xml:space="preserve">Rødkløvervej 4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422741</t>
+          <t xml:space="preserve">9379331</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>390</v>
+        <v>1290</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011821</t>
+          <t xml:space="preserve">200013233</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-05-04</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 11</t>
+          <t xml:space="preserve">Søibergsvej 4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726355</t>
+          <t xml:space="preserve">5726631</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>529</v>
+        <v>225</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011832</t>
+          <t xml:space="preserve">200014305</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-05-29</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,17 +17066,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 22</t>
+          <t xml:space="preserve">Klostervej 39</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">9670777</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,11 +17085,11 @@
         </is>
       </c>
       <c r="J228">
-        <v>179</v>
+        <v>2672</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011880</t>
+          <t xml:space="preserve">200014492</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthaabsvej 8</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725086</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>746</v>
+        <v>3316</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011892</t>
+          <t xml:space="preserve">200014523</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-06-04</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelvej 39A</t>
+          <t xml:space="preserve">Kongevejen 1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419782</t>
+          <t xml:space="preserve">5724668</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,21 +17235,21 @@
         </is>
       </c>
       <c r="J230">
-        <v>419</v>
+        <v>380</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012873</t>
+          <t xml:space="preserve">200014705</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 22</t>
+          <t xml:space="preserve">Lønhøjvej 38</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8161686</t>
+          <t xml:space="preserve">4468081</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>314</v>
+        <v>837</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012912</t>
+          <t xml:space="preserve">200014740</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidkløvervej 8</t>
+          <t xml:space="preserve">Engdraget 4</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430418</t>
+          <t xml:space="preserve">4468323</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>311</v>
+        <v>614</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012910</t>
+          <t xml:space="preserve">200015083</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,17 +17441,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 31</t>
+          <t xml:space="preserve">Egevej 5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726882</t>
+          <t xml:space="preserve">4468558</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,21 +17460,21 @@
         </is>
       </c>
       <c r="J233">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012988</t>
+          <t xml:space="preserve">100124780</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 7</t>
+          <t xml:space="preserve">Enghavevej 49</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724932</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,21 +17535,21 @@
         </is>
       </c>
       <c r="J234">
-        <v>216</v>
+        <v>123</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012990</t>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskellet 20</t>
+          <t xml:space="preserve">Parallelvej 100</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725537</t>
+          <t xml:space="preserve">8043441</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,11 +17610,11 @@
         </is>
       </c>
       <c r="J235">
-        <v>1556</v>
+        <v>3650</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013034</t>
+          <t xml:space="preserve">200015550</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,17 +17666,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 9</t>
+          <t xml:space="preserve">Søndergade 67</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792930</t>
+          <t xml:space="preserve">4480605</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="J236">
-        <v>356</v>
+        <v>132</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013038</t>
+          <t xml:space="preserve">100124985</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fischersvej 6</t>
+          <t xml:space="preserve">Søndergade 69</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483012</t>
+          <t xml:space="preserve">4480604</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17760,21 +17760,21 @@
         </is>
       </c>
       <c r="J237">
-        <v>848</v>
+        <v>130</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012993</t>
+          <t xml:space="preserve">100124968</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødkløvervej 4</t>
+          <t xml:space="preserve">Nylandsvej 10</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9379331</t>
+          <t xml:space="preserve">5788092</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,11 +17835,11 @@
         </is>
       </c>
       <c r="J238">
-        <v>1290</v>
+        <v>284</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013233</t>
+          <t xml:space="preserve">200016205</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-04</t>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,40 +17891,40 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 4</t>
+          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726631</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J239">
-        <v>225</v>
+        <v>995</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014305</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-29</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,40 +17966,40 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 39</t>
+          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">9670777</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J240">
-        <v>2672</v>
+        <v>1395</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014492</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,40 +18041,40 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Kirkegade 3B</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J241">
-        <v>3316</v>
+        <v>2716</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014523</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-04</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,40 +18116,40 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 1</t>
+          <t xml:space="preserve">Kirkegade 3C</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724668</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J242">
-        <v>380</v>
+        <v>246</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014705</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønhøjvej 38</t>
+          <t xml:space="preserve">Kirkegade 3B</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468081</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -18210,21 +18210,21 @@
         </is>
       </c>
       <c r="J243">
-        <v>837</v>
+        <v>756</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014740</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 4</t>
+          <t xml:space="preserve">Kirkegade 5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,30 +18276,30 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468323</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J244">
-        <v>614</v>
+        <v>1725</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015083</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-16</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,17 +18341,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 5</t>
+          <t xml:space="preserve">Kongevejen 52A</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468558</t>
+          <t xml:space="preserve">5725835</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,21 +18360,21 @@
         </is>
       </c>
       <c r="J245">
-        <v>195</v>
+        <v>2126</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124780</t>
+          <t xml:space="preserve">200054663</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 49</t>
+          <t xml:space="preserve">Midtbyvej 32</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">746271, 4473222</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J246">
-        <v>123</v>
+        <v>2466</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124776</t>
+          <t xml:space="preserve">200057628</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Botjek Odense a/s</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 100</t>
+          <t xml:space="preserve">Tylvadvej 2A</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043441</t>
+          <t xml:space="preserve">4480225</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>3650</v>
+        <v>3911</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015550</t>
+          <t xml:space="preserve">200058806</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">EnergiMidt</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2022-04-12</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,40 +18566,40 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 67</t>
+          <t xml:space="preserve">Fredensgade 28</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480605</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J248">
-        <v>132</v>
+        <v>1346</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124985</t>
+          <t xml:space="preserve">310011917</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2022-11-05</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,17 +18641,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 69</t>
+          <t xml:space="preserve">Tinghusvej 4</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480604</t>
+          <t xml:space="preserve">5787947</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -18660,21 +18660,21 @@
         </is>
       </c>
       <c r="J249">
-        <v>130</v>
+        <v>1199</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124968</t>
+          <t xml:space="preserve">310034028</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Botjek Skive</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2023-04-09</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,17 +18716,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 10</t>
+          <t xml:space="preserve">Reberbanen 32</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788092</t>
+          <t xml:space="preserve">5724799</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -18735,21 +18735,21 @@
         </is>
       </c>
       <c r="J250">
-        <v>284</v>
+        <v>376</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016205</t>
+          <t xml:space="preserve">311138690</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2024-07-08</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
+          <t xml:space="preserve">Østerbyvej 3B</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,20 +18801,20 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>995</v>
+        <v>166</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">311125157</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2025-07-15</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,40 +18866,40 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
+          <t xml:space="preserve">Holmegaardsbakken 4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">100065998</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>1395</v>
+        <v>898</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">311142678</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2025-10-30</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3B</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>2716</v>
+        <v>1089</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">311168902</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,40 +19016,40 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3C</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">746431, 5725289</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J254">
-        <v>246</v>
+        <v>2061</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">311169247</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3B</t>
+          <t xml:space="preserve">Smed Sørensens Vej 5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">746461, 5725289</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J255">
-        <v>756</v>
+        <v>1794</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">311169248</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,40 +19166,40 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 5</t>
+          <t xml:space="preserve">E F Jacobsens Vej 7</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">746486, 8918730</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J256">
-        <v>1725</v>
+        <v>3892</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">311169525</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 52A</t>
+          <t xml:space="preserve">Smed Sørensens Vej 6</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,30 +19251,30 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725835</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J257">
-        <v>2126</v>
+        <v>2534</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054663</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 32</t>
+          <t xml:space="preserve">Smed Sørensens Vej 6</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">746271, 4473222</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="J258">
-        <v>2466</v>
+        <v>1249</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057628</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Odense a/s</t>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19376,12 +19376,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">Hee Sogneforening</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -19391,50 +19391,50 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2A</t>
+          <t xml:space="preserve">Agersbækvej 13</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480225</t>
+          <t xml:space="preserve">335013, 335014</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J259">
-        <v>3911</v>
+        <v>779</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058806</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiMidt</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-12</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19466,50 +19466,50 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensgade 28</t>
+          <t xml:space="preserve">Agersbækvej 15</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>1346</v>
+        <v>1514</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">310011917</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-05</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19541,50 +19541,50 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusvej 4</t>
+          <t xml:space="preserve">Agersbækvej 15</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787947</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J261">
-        <v>1199</v>
+        <v>917</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034028</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Skive</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-09</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19616,17 +19616,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reberbanen 32</t>
+          <t xml:space="preserve">Algade 63</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724799</t>
+          <t xml:space="preserve">9676000</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,31 +19635,31 @@
         </is>
       </c>
       <c r="J262">
-        <v>376</v>
+        <v>1571</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138690</t>
+          <t xml:space="preserve">311260252</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-08</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19691,17 +19691,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbyvej 3B</t>
+          <t xml:space="preserve">Herningvej 107</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">4429258</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -19710,31 +19710,31 @@
         </is>
       </c>
       <c r="J263">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311125157</t>
+          <t xml:space="preserve">311260253</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-15</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 4</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">100065998</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,31 +19785,31 @@
         </is>
       </c>
       <c r="J264">
-        <v>898</v>
+        <v>740</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142678</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-30</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19841,30 +19841,30 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J265">
-        <v>1089</v>
+        <v>1407</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168902</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,17 +19874,17 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-07</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,40 +19926,40 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">746431, 5725289</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J266">
-        <v>2061</v>
+        <v>8851</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169247</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 5</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,40 +20001,40 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">746461, 5725289</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J267">
-        <v>1794</v>
+        <v>3739</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169248</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -20066,50 +20066,50 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">E F Jacobsens Vej 7</t>
+          <t xml:space="preserve">Bardevej 5</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">746486, 8918730</t>
+          <t xml:space="preserve">4487058</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J268">
-        <v>3892</v>
+        <v>2298</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169525</t>
+          <t xml:space="preserve">311267783</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -20141,50 +20141,50 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 6</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J269">
-        <v>2534</v>
+        <v>525</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169524</t>
+          <t xml:space="preserve">311267663</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -20216,50 +20216,50 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 6</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J270">
-        <v>1249</v>
+        <v>198</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169524</t>
+          <t xml:space="preserve">311288413</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -20276,12 +20276,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hee Sogneforening</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 13</t>
+          <t xml:space="preserve">Klostervej 87</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,30 +20301,30 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">335013, 335014</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J271">
-        <v>779</v>
+        <v>165</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311311426</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2028-05-01</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,17 +20366,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 15</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20385,21 +20385,21 @@
         </is>
       </c>
       <c r="J272">
-        <v>1514</v>
+        <v>2956</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 15</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,21 +20460,21 @@
         </is>
       </c>
       <c r="J273">
-        <v>917</v>
+        <v>1297</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,40 +20516,40 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 63</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676000</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J274">
-        <v>1571</v>
+        <v>1261</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260252</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,40 +20591,40 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 107</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429258</t>
+          <t xml:space="preserve">338783</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J275">
-        <v>211</v>
+        <v>749</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260253</t>
+          <t xml:space="preserve">311378684</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,17 +20666,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Vardevej 47A</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,21 +20685,21 @@
         </is>
       </c>
       <c r="J276">
-        <v>740</v>
+        <v>620</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311378685</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,40 +20741,40 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Lunden 1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J277">
-        <v>1407</v>
+        <v>2236</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311389424</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,40 +20816,40 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Lunden 1</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J278">
-        <v>8851</v>
+        <v>453</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311389426</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20901,30 +20901,30 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J279">
-        <v>3739</v>
+        <v>1856</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,40 +20966,40 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bardevej 5</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487058</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J280">
-        <v>2298</v>
+        <v>2960</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267783</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,40 +21041,40 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J281">
-        <v>525</v>
+        <v>1091</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267663</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,40 +21116,40 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J282">
-        <v>198</v>
+        <v>380</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288413</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 87</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21201,30 +21201,30 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J283">
-        <v>165</v>
+        <v>474</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311426</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-01</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,30 +21266,30 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J284">
-        <v>2956</v>
+        <v>447</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,30 +21341,30 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Tøstrupvej 26</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J285">
-        <v>1297</v>
+        <v>2185</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,20 +21426,20 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J286">
-        <v>1261</v>
+        <v>655</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21501,20 +21501,20 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">338783</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J287">
-        <v>749</v>
+        <v>262</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378684</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,40 +21566,40 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 47A</t>
+          <t xml:space="preserve">Engdraget 24A</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J288">
-        <v>620</v>
+        <v>390</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378685</t>
+          <t xml:space="preserve">311419880</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,40 +21641,40 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunden 1</t>
+          <t xml:space="preserve">Engdraget 26A</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J289">
-        <v>2236</v>
+        <v>390</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389424</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,40 +21716,40 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunden 1</t>
+          <t xml:space="preserve">Bindesbølvej 2</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">4466575</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J290">
-        <v>453</v>
+        <v>209</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389426</t>
+          <t xml:space="preserve">311424214</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,17 +21791,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Skjernåvej 4A</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -21810,21 +21810,21 @@
         </is>
       </c>
       <c r="J291">
-        <v>1856</v>
+        <v>399</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311424140</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,40 +21866,40 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Svinget 5</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J292">
-        <v>2960</v>
+        <v>392</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,17 +21941,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Svinget 5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -21960,21 +21960,21 @@
         </is>
       </c>
       <c r="J293">
-        <v>1091</v>
+        <v>703</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,40 +22016,40 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Centerparken 1</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">9701346</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J294">
-        <v>380</v>
+        <v>4482</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311552774</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,40 +22091,40 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Jægervej 13</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J295">
-        <v>474</v>
+        <v>1557</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,40 +22166,40 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Lærkevænget 1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J296">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,17 +22241,17 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøstrupvej 26</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -22260,21 +22260,21 @@
         </is>
       </c>
       <c r="J297">
-        <v>2185</v>
+        <v>1060</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311555859</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,17 +22316,17 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,21 +22335,21 @@
         </is>
       </c>
       <c r="J298">
-        <v>655</v>
+        <v>606</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311561693</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22391,40 +22391,40 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Storegade 40</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">4467758</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J299">
-        <v>262</v>
+        <v>401</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311599352</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22466,40 +22466,40 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 24A</t>
+          <t xml:space="preserve">Åvænget 3A</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">100145225</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>390</v>
+        <v>810</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419880</t>
+          <t xml:space="preserve">311582272</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 26A</t>
+          <t xml:space="preserve">Nygade 1</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,30 +22551,30 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">4467959</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J301">
-        <v>390</v>
+        <v>308</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311598466</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -22601,12 +22601,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -22616,40 +22616,40 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbølvej 2</t>
+          <t xml:space="preserve">Vesterled 6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466575</t>
+          <t xml:space="preserve">746440, 7003908</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J302">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424214</t>
+          <t xml:space="preserve">311605015</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,17 +22691,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjernåvej 4A</t>
+          <t xml:space="preserve">Midtbyvej 30</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">7662602</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,21 +22710,21 @@
         </is>
       </c>
       <c r="J303">
-        <v>399</v>
+        <v>1817</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424140</t>
+          <t xml:space="preserve">311650708</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">MST-Bygtjek ApS</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,30 +22766,30 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 5</t>
+          <t xml:space="preserve">Holmegaardsbakken 18</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">335032</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J304">
-        <v>392</v>
+        <v>116</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311653077</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">bomidtvest</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -22841,30 +22841,30 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 5</t>
+          <t xml:space="preserve">Tarmvej 99</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">337849, 337850</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J305">
-        <v>703</v>
+        <v>878</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311668912</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22916,40 +22916,40 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centerparken 1</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">9701346</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J306">
-        <v>4482</v>
+        <v>99</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552774</t>
+          <t xml:space="preserve">311679352</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-04</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,40 +22991,40 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 13</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J307">
-        <v>1557</v>
+        <v>100</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevænget 1</t>
+          <t xml:space="preserve">Ranunkelvej 11A</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23076,30 +23076,30 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">5790131, 100782857</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J308">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311689382</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23141,40 +23141,40 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Skolebakken 20</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">746445, 4419703</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J309">
-        <v>1060</v>
+        <v>3326</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555859</t>
+          <t xml:space="preserve">311883390</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2036-02-21</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23216,40 +23216,40 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J310">
-        <v>606</v>
+        <v>1345</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561693</t>
+          <t xml:space="preserve">311886105</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-13</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -23301,30 +23301,30 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467758</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J311">
-        <v>401</v>
+        <v>2810</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599352</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23366,40 +23366,40 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åvænget 3A</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">100145225</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J312">
-        <v>810</v>
+        <v>1725</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582272</t>
+          <t xml:space="preserve">311886107</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 1</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23451,30 +23451,30 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467959</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J313">
-        <v>308</v>
+        <v>1360</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598466</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23501,12 +23501,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 6</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,30 +23526,30 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">746440, 7003908</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J314">
-        <v>146</v>
+        <v>703</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605015</t>
+          <t xml:space="preserve">311889055</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,17 +23591,17 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 30</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7662602</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -23610,21 +23610,21 @@
         </is>
       </c>
       <c r="J315">
-        <v>1817</v>
+        <v>125</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650708</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">MST-Bygtjek ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,40 +23666,40 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 18</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">335032</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J316">
-        <v>116</v>
+        <v>766</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653077</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23726,12 +23726,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">bomidtvest</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -23741,40 +23741,40 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarmvej 99</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">337849, 337850</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J317">
-        <v>878</v>
+        <v>241</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668912</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,40 +23816,40 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J318">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679352</t>
+          <t xml:space="preserve">311892268</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,21 +23910,21 @@
         </is>
       </c>
       <c r="J319">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679351</t>
+          <t xml:space="preserve">311892268</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,40 +23966,40 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 11A</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131, 100782857</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J320">
-        <v>414</v>
+        <v>2123</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689382</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,40 +24041,40 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 20</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">746445, 4419703</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J321">
-        <v>3326</v>
+        <v>915</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883390</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-21</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,40 +24116,40 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J322">
-        <v>1345</v>
+        <v>616</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886105</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,40 +24191,40 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J323">
-        <v>2810</v>
+        <v>1810</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J324">
-        <v>1725</v>
+        <v>125</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886107</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,40 +24341,40 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J325">
-        <v>1360</v>
+        <v>128</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,40 +24416,40 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">746506, 4477641</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J326">
-        <v>703</v>
+        <v>2072</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311889055</t>
+          <t xml:space="preserve">311892347</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,17 +24491,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Ågade 12</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -24510,16 +24510,16 @@
         </is>
       </c>
       <c r="J327">
-        <v>125</v>
+        <v>729</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -24566,17 +24566,17 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -24585,16 +24585,16 @@
         </is>
       </c>
       <c r="J328">
-        <v>766</v>
+        <v>729</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -24641,40 +24641,40 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Badevej 17A</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">4421290, 100992804</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J329">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311900271</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-05-10</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -24716,30 +24716,30 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J330">
-        <v>170</v>
+        <v>788</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311929041</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -24791,22 +24791,22 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Kjærgaardsvej 10</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">746491, 8463749</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J331">
@@ -24814,17 +24814,17 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24866,17 +24866,17 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -24885,21 +24885,21 @@
         </is>
       </c>
       <c r="J332">
-        <v>2123</v>
+        <v>230</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -24941,40 +24941,40 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J333">
-        <v>915</v>
+        <v>232</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25016,40 +25016,40 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J334">
-        <v>616</v>
+        <v>232</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25091,40 +25091,40 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J335">
-        <v>1810</v>
+        <v>232</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,40 +25166,40 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J336">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,40 +25241,40 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J337">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -25316,40 +25316,40 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">746506, 4477641</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J338">
-        <v>2072</v>
+        <v>178</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892347</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25391,40 +25391,40 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 12</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J339">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -25466,17 +25466,17 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -25485,21 +25485,21 @@
         </is>
       </c>
       <c r="J340">
-        <v>729</v>
+        <v>153</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Badevej 17A</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,30 +25551,30 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421290, 100992804</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J341">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900271</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-10</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,17 +25616,17 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -25635,21 +25635,21 @@
         </is>
       </c>
       <c r="J342">
-        <v>788</v>
+        <v>237</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929041</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
